--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +948,510 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:37</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:37</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:37</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:37</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:37</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:38</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:38</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:38</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:38</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:38</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:39</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:39</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:39</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:39</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:40</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:42</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:44</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:45</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:45</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-10 11:45</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,6 +948,510 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:41</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:41</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:41</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:41</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:42</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:42</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:42</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:42</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:42</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:43</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:43</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:43</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:43</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:44</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:44</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:46</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:49</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:49</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:49</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-11 11:49</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historial_precios.xlsx
+++ b/historial_precios.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1452,6 +1452,510 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:53</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-fino-negro-cajilla-12-piezas-7501014511061/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:53</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>10049</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-fine-os-negro-12-piezas-7703486011661/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:54</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>12849</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-azor-fino-pin-point-negro-12-piezas-7501428727195/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:54</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-bic-punto-mediano10-mm-negro-cajilla-12-piezas-7501014511023/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:54</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-kilometrico-100-negro-caja-con-12-piezas-7703486035339/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:54</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>12844</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianonegro-12-piezas-azor-transparente-7501428727249/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:54</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>12848</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/boligrafo-medianosurtido-roazneg-12-piezas-transparente-7501428727263/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:55</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>3902</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cinta-transparente-janel-18x33-pieza-7501035112698/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:55</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>474</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-36-piezas-7702111261143/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:55</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>259</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-de-244l-7702111817494/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:55</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/colores-norma-x-14-15-triangulares-7702111500778/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:55</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>229</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-24-pzas-70530014860/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:56</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/lapices-de-colores-prismacolor-junior-redondo-12-pzas-70530014815/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:56</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1576</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/cuaderno-profesional-cuadro-grande-norma-color-100-hojas-500744451/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:56</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>299</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/caja-con-100-lapices-de-grafito-no2-metrico-dixon-7501147419036/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-12 10:59</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1233</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-fotobond-95--blancura-500-hojas-7502233377537/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:01</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/paquetes-de-hojas-tama%C3%B1o-carta-scribe-ecologico-93--blancura-500-hojas-7502233377797/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:01</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-escolar-azul-pastel-100-ml-316-tono-suave-501369321/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:01</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>94</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/pintura-acrilica-politec-302-negro-intenso-250ml-7501230030247/p</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:02</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>3823</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.officemax.com.mx/registrador-lefort-tamano-carta-verde-lefort-7501434711270/p</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
